--- a/artfynd/A 47442-2025 artfynd.xlsx
+++ b/artfynd/A 47442-2025 artfynd.xlsx
@@ -3034,50 +3034,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129128638</v>
+        <v>129128675</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>79063</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446029</v>
+        <v>445750</v>
       </c>
       <c r="R24" t="n">
-        <v>6821503</v>
+        <v>6821192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,32 +3141,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129128675</v>
+        <v>129128859</v>
       </c>
       <c r="B25" t="n">
-        <v>79063</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445750</v>
+        <v>445989</v>
       </c>
       <c r="R25" t="n">
-        <v>6821192</v>
+        <v>6821072</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129128859</v>
+        <v>129128694</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445989</v>
+        <v>445659</v>
       </c>
       <c r="R26" t="n">
-        <v>6821072</v>
+        <v>6821135</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,22 +3313,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3360,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129128694</v>
+        <v>129128856</v>
       </c>
       <c r="B27" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445659</v>
+        <v>446003</v>
       </c>
       <c r="R27" t="n">
-        <v>6821135</v>
+        <v>6821065</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,22 +3420,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,7 +3462,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129128856</v>
+        <v>129128864</v>
       </c>
       <c r="B28" t="n">
         <v>79039</v>
@@ -3502,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446003</v>
+        <v>445863</v>
       </c>
       <c r="R28" t="n">
-        <v>6821065</v>
+        <v>6821092</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3532,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3547,7 +3542,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3574,7 +3569,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129128864</v>
+        <v>129128999</v>
       </c>
       <c r="B29" t="n">
         <v>79039</v>
@@ -3609,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445863</v>
+        <v>446274</v>
       </c>
       <c r="R29" t="n">
-        <v>6821092</v>
+        <v>6821311</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3639,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3654,7 +3649,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3681,10 +3676,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129128999</v>
+        <v>129128638</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,34 +3687,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446274</v>
+        <v>446029</v>
       </c>
       <c r="R30" t="n">
-        <v>6821311</v>
+        <v>6821503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4760,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129128730</v>
+        <v>129128998</v>
       </c>
       <c r="B40" t="n">
-        <v>56906</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4771,42 +4771,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445745</v>
+        <v>446315</v>
       </c>
       <c r="R40" t="n">
-        <v>6821055</v>
+        <v>6821299</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4838,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4848,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4875,7 +4867,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129128998</v>
+        <v>129128809</v>
       </c>
       <c r="B41" t="n">
         <v>79039</v>
@@ -4910,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446315</v>
+        <v>445853</v>
       </c>
       <c r="R41" t="n">
-        <v>6821299</v>
+        <v>6820984</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4945,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4955,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4982,7 +4974,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129128809</v>
+        <v>129128975</v>
       </c>
       <c r="B42" t="n">
         <v>79039</v>
@@ -5017,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445853</v>
+        <v>446455</v>
       </c>
       <c r="R42" t="n">
-        <v>6820984</v>
+        <v>6821329</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5052,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5062,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5089,7 +5081,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129128975</v>
+        <v>129128915</v>
       </c>
       <c r="B43" t="n">
         <v>79039</v>
@@ -5124,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446455</v>
+        <v>446279</v>
       </c>
       <c r="R43" t="n">
-        <v>6821329</v>
+        <v>6821592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5169,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5196,7 +5188,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129128915</v>
+        <v>129128925</v>
       </c>
       <c r="B44" t="n">
         <v>79039</v>
@@ -5231,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446279</v>
+        <v>446297</v>
       </c>
       <c r="R44" t="n">
-        <v>6821592</v>
+        <v>6821509</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5266,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5276,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5303,7 +5295,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129128925</v>
+        <v>129128858</v>
       </c>
       <c r="B45" t="n">
         <v>79039</v>
@@ -5338,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446297</v>
+        <v>445990</v>
       </c>
       <c r="R45" t="n">
-        <v>6821509</v>
+        <v>6821060</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5373,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5383,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5410,10 +5402,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129128858</v>
+        <v>129129051</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5421,34 +5413,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445990</v>
+        <v>446456</v>
       </c>
       <c r="R46" t="n">
-        <v>6821060</v>
+        <v>6821328</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5480,7 +5477,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5490,7 +5487,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5517,10 +5514,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129129051</v>
+        <v>129128730</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>56906</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5528,16 +5525,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5546,21 +5543,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446456</v>
+        <v>445745</v>
       </c>
       <c r="R47" t="n">
-        <v>6821328</v>
+        <v>6821055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5629,45 +5629,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129128663</v>
+        <v>129128708</v>
       </c>
       <c r="B48" t="n">
-        <v>97540</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445974</v>
+        <v>446496</v>
       </c>
       <c r="R48" t="n">
-        <v>6821028</v>
+        <v>6821199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5699,7 +5708,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5709,7 +5718,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5736,7 +5745,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129128664</v>
+        <v>129128663</v>
       </c>
       <c r="B49" t="n">
         <v>97540</v>
@@ -5771,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445913</v>
+        <v>445974</v>
       </c>
       <c r="R49" t="n">
-        <v>6821060</v>
+        <v>6821028</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5806,7 +5815,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5816,7 +5825,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5843,54 +5852,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129128708</v>
+        <v>129128664</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>97540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446496</v>
+        <v>445913</v>
       </c>
       <c r="R50" t="n">
-        <v>6821199</v>
+        <v>6821060</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -8891,45 +8891,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129128671</v>
+        <v>129129050</v>
       </c>
       <c r="B78" t="n">
-        <v>97546</v>
+        <v>57725</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446369</v>
+        <v>446403</v>
       </c>
       <c r="R78" t="n">
-        <v>6821371</v>
+        <v>6821456</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8961,7 +8966,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8971,7 +8976,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8998,45 +9003,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129128666</v>
+        <v>129129044</v>
       </c>
       <c r="B79" t="n">
-        <v>97540</v>
+        <v>57725</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445928</v>
+        <v>446474</v>
       </c>
       <c r="R79" t="n">
-        <v>6821478</v>
+        <v>6821207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9068,7 +9078,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9078,7 +9088,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9105,45 +9115,59 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129128670</v>
+        <v>129128699</v>
       </c>
       <c r="B80" t="n">
-        <v>97540</v>
+        <v>98669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>446191</v>
+        <v>446046</v>
       </c>
       <c r="R80" t="n">
-        <v>6821181</v>
+        <v>6821156</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9175,7 +9199,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9185,7 +9209,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9212,38 +9236,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129129050</v>
+        <v>129128727</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9252,10 +9280,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>446403</v>
+        <v>445988</v>
       </c>
       <c r="R81" t="n">
-        <v>6821456</v>
+        <v>6821075</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9287,7 +9315,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9297,7 +9325,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9324,50 +9352,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129129044</v>
+        <v>129128671</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>97546</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446474</v>
+        <v>446369</v>
       </c>
       <c r="R82" t="n">
-        <v>6821207</v>
+        <v>6821371</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9399,7 +9422,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9409,7 +9432,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9436,59 +9459,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129128699</v>
+        <v>129128666</v>
       </c>
       <c r="B83" t="n">
-        <v>98669</v>
+        <v>97540</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446046</v>
+        <v>445928</v>
       </c>
       <c r="R83" t="n">
-        <v>6821156</v>
+        <v>6821478</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9520,7 +9529,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9530,7 +9539,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9557,54 +9566,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129128727</v>
+        <v>129128670</v>
       </c>
       <c r="B84" t="n">
-        <v>98669</v>
+        <v>97540</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445988</v>
+        <v>446191</v>
       </c>
       <c r="R84" t="n">
-        <v>6821075</v>
+        <v>6821181</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12907,54 +12907,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129128723</v>
+        <v>129128823</v>
       </c>
       <c r="B115" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>446373</v>
+        <v>445868</v>
       </c>
       <c r="R115" t="n">
-        <v>6821433</v>
+        <v>6821020</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12986,7 +12977,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12996,7 +12987,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13023,54 +13014,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129128726</v>
+        <v>129128917</v>
       </c>
       <c r="B116" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>446032</v>
+        <v>446281</v>
       </c>
       <c r="R116" t="n">
-        <v>6821151</v>
+        <v>6821643</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13102,7 +13084,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13112,7 +13094,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13139,54 +13121,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129128705</v>
+        <v>129128981</v>
       </c>
       <c r="B117" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>446325</v>
+        <v>446557</v>
       </c>
       <c r="R117" t="n">
-        <v>6821299</v>
+        <v>6821296</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13218,7 +13191,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13228,7 +13201,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13255,7 +13228,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129128823</v>
+        <v>129128903</v>
       </c>
       <c r="B118" t="n">
         <v>79039</v>
@@ -13290,10 +13263,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445868</v>
+        <v>446052</v>
       </c>
       <c r="R118" t="n">
-        <v>6821020</v>
+        <v>6821517</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13325,7 +13298,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13335,7 +13308,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13362,7 +13335,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129128917</v>
+        <v>129128875</v>
       </c>
       <c r="B119" t="n">
         <v>79039</v>
@@ -13397,10 +13370,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>446281</v>
+        <v>445716</v>
       </c>
       <c r="R119" t="n">
-        <v>6821643</v>
+        <v>6821171</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13432,7 +13405,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13442,7 +13415,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13469,45 +13442,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129128981</v>
+        <v>129128726</v>
       </c>
       <c r="B120" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>446557</v>
+        <v>446032</v>
       </c>
       <c r="R120" t="n">
-        <v>6821296</v>
+        <v>6821151</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13539,7 +13521,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13549,7 +13531,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13576,45 +13558,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129128903</v>
+        <v>129128705</v>
       </c>
       <c r="B121" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>446052</v>
+        <v>446325</v>
       </c>
       <c r="R121" t="n">
-        <v>6821517</v>
+        <v>6821299</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13646,7 +13637,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13656,7 +13647,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13683,7 +13674,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129128875</v>
+        <v>129128849</v>
       </c>
       <c r="B122" t="n">
         <v>79039</v>
@@ -13718,10 +13709,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445716</v>
+        <v>446022</v>
       </c>
       <c r="R122" t="n">
-        <v>6821171</v>
+        <v>6821033</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13753,7 +13744,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13763,7 +13754,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13790,10 +13781,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129128849</v>
+        <v>129128597</v>
       </c>
       <c r="B123" t="n">
-        <v>79039</v>
+        <v>83015</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13801,21 +13792,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13825,10 +13816,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>446022</v>
+        <v>445731</v>
       </c>
       <c r="R123" t="n">
-        <v>6821033</v>
+        <v>6821175</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13855,22 +13846,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13897,7 +13888,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129128597</v>
+        <v>129128598</v>
       </c>
       <c r="B124" t="n">
         <v>83015</v>
@@ -13932,10 +13923,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445731</v>
+        <v>445995</v>
       </c>
       <c r="R124" t="n">
-        <v>6821175</v>
+        <v>6821060</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13962,22 +13953,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14004,10 +13995,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129128598</v>
+        <v>129128965</v>
       </c>
       <c r="B125" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14015,21 +14006,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14039,10 +14030,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445995</v>
+        <v>446418</v>
       </c>
       <c r="R125" t="n">
-        <v>6821060</v>
+        <v>6821351</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14074,7 +14065,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14084,7 +14075,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14111,7 +14102,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129128965</v>
+        <v>129128810</v>
       </c>
       <c r="B126" t="n">
         <v>79039</v>
@@ -14146,10 +14137,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>446418</v>
+        <v>445848</v>
       </c>
       <c r="R126" t="n">
-        <v>6821351</v>
+        <v>6820984</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14181,7 +14172,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14191,7 +14182,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14218,32 +14209,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129128810</v>
+        <v>129128660</v>
       </c>
       <c r="B127" t="n">
-        <v>79039</v>
+        <v>97540</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14253,10 +14244,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445848</v>
+        <v>446283</v>
       </c>
       <c r="R127" t="n">
-        <v>6820984</v>
+        <v>6821628</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14288,7 +14279,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14298,7 +14289,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14325,45 +14316,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129128660</v>
+        <v>129128723</v>
       </c>
       <c r="B128" t="n">
-        <v>97540</v>
+        <v>98669</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>446283</v>
+        <v>446373</v>
       </c>
       <c r="R128" t="n">
-        <v>6821628</v>
+        <v>6821433</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15743,7 +15743,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129128928</v>
+        <v>129128847</v>
       </c>
       <c r="B141" t="n">
         <v>79039</v>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>446368</v>
+        <v>446012</v>
       </c>
       <c r="R141" t="n">
-        <v>6821499</v>
+        <v>6821005</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15850,7 +15850,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129128983</v>
+        <v>129128783</v>
       </c>
       <c r="B142" t="n">
         <v>79039</v>
@@ -15885,10 +15885,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>446559</v>
+        <v>445691</v>
       </c>
       <c r="R142" t="n">
-        <v>6821268</v>
+        <v>6821290</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15915,22 +15915,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15957,7 +15957,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129128891</v>
+        <v>129128976</v>
       </c>
       <c r="B143" t="n">
         <v>79039</v>
@@ -15992,10 +15992,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445929</v>
+        <v>446465</v>
       </c>
       <c r="R143" t="n">
-        <v>6821478</v>
+        <v>6821340</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16064,7 +16064,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129128873</v>
+        <v>129128869</v>
       </c>
       <c r="B144" t="n">
         <v>79039</v>
@@ -16099,10 +16099,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445732</v>
+        <v>445743</v>
       </c>
       <c r="R144" t="n">
-        <v>6821157</v>
+        <v>6821128</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16171,7 +16171,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129128803</v>
+        <v>129128994</v>
       </c>
       <c r="B145" t="n">
         <v>79039</v>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445887</v>
+        <v>446398</v>
       </c>
       <c r="R145" t="n">
-        <v>6820940</v>
+        <v>6821295</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16278,7 +16278,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129128847</v>
+        <v>129128928</v>
       </c>
       <c r="B146" t="n">
         <v>79039</v>
@@ -16313,10 +16313,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>446012</v>
+        <v>446368</v>
       </c>
       <c r="R146" t="n">
-        <v>6821005</v>
+        <v>6821499</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16385,7 +16385,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129128783</v>
+        <v>129128983</v>
       </c>
       <c r="B147" t="n">
         <v>79039</v>
@@ -16420,10 +16420,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445691</v>
+        <v>446559</v>
       </c>
       <c r="R147" t="n">
-        <v>6821290</v>
+        <v>6821268</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16492,7 +16492,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129128976</v>
+        <v>129128891</v>
       </c>
       <c r="B148" t="n">
         <v>79039</v>
@@ -16527,10 +16527,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>446465</v>
+        <v>445929</v>
       </c>
       <c r="R148" t="n">
-        <v>6821340</v>
+        <v>6821478</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16599,7 +16599,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129128869</v>
+        <v>129128873</v>
       </c>
       <c r="B149" t="n">
         <v>79039</v>
@@ -16634,10 +16634,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445743</v>
+        <v>445732</v>
       </c>
       <c r="R149" t="n">
-        <v>6821128</v>
+        <v>6821157</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16706,7 +16706,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129128994</v>
+        <v>129128803</v>
       </c>
       <c r="B150" t="n">
         <v>79039</v>
@@ -16741,10 +16741,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>446398</v>
+        <v>445887</v>
       </c>
       <c r="R150" t="n">
-        <v>6821295</v>
+        <v>6820940</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16813,7 +16813,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129129048</v>
+        <v>129129049</v>
       </c>
       <c r="B151" t="n">
         <v>57725</v>
@@ -16853,10 +16853,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>446482</v>
+        <v>446437</v>
       </c>
       <c r="R151" t="n">
-        <v>6821467</v>
+        <v>6821476</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16925,45 +16925,54 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129128942</v>
+        <v>129128713</v>
       </c>
       <c r="B152" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>446437</v>
+        <v>445994</v>
       </c>
       <c r="R152" t="n">
-        <v>6821476</v>
+        <v>6821055</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16995,7 +17004,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17005,7 +17014,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17032,10 +17041,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129128603</v>
+        <v>129129048</v>
       </c>
       <c r="B153" t="n">
-        <v>83015</v>
+        <v>57725</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17043,34 +17052,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>446292</v>
+        <v>446482</v>
       </c>
       <c r="R153" t="n">
-        <v>6821612</v>
+        <v>6821467</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17102,7 +17116,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17112,7 +17126,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17139,7 +17153,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129128846</v>
+        <v>129128942</v>
       </c>
       <c r="B154" t="n">
         <v>79039</v>
@@ -17174,10 +17188,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>446001</v>
+        <v>446437</v>
       </c>
       <c r="R154" t="n">
-        <v>6821010</v>
+        <v>6821476</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17209,7 +17223,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17219,7 +17233,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17246,10 +17260,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129128910</v>
+        <v>129128603</v>
       </c>
       <c r="B155" t="n">
-        <v>79039</v>
+        <v>83015</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17257,21 +17271,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17281,10 +17295,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>446195</v>
+        <v>446292</v>
       </c>
       <c r="R155" t="n">
-        <v>6821599</v>
+        <v>6821612</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17316,7 +17330,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17326,7 +17340,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17353,7 +17367,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129128995</v>
+        <v>129128846</v>
       </c>
       <c r="B156" t="n">
         <v>79039</v>
@@ -17388,10 +17402,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>446393</v>
+        <v>446001</v>
       </c>
       <c r="R156" t="n">
-        <v>6821303</v>
+        <v>6821010</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17423,7 +17437,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17433,7 +17447,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17460,7 +17474,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129128886</v>
+        <v>129128910</v>
       </c>
       <c r="B157" t="n">
         <v>79039</v>
@@ -17495,10 +17509,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>445782</v>
+        <v>446195</v>
       </c>
       <c r="R157" t="n">
-        <v>6821410</v>
+        <v>6821599</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17530,7 +17544,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17540,7 +17554,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17567,7 +17581,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129128872</v>
+        <v>129128995</v>
       </c>
       <c r="B158" t="n">
         <v>79039</v>
@@ -17602,10 +17616,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>445721</v>
+        <v>446393</v>
       </c>
       <c r="R158" t="n">
-        <v>6821142</v>
+        <v>6821303</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17637,7 +17651,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17647,7 +17661,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17674,7 +17688,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129128817</v>
+        <v>129128886</v>
       </c>
       <c r="B159" t="n">
         <v>79039</v>
@@ -17709,10 +17723,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>445832</v>
+        <v>445782</v>
       </c>
       <c r="R159" t="n">
-        <v>6820988</v>
+        <v>6821410</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17744,7 +17758,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17754,7 +17768,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17781,7 +17795,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129128754</v>
+        <v>129128872</v>
       </c>
       <c r="B160" t="n">
         <v>79039</v>
@@ -17816,10 +17830,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>445736</v>
+        <v>445721</v>
       </c>
       <c r="R160" t="n">
-        <v>6821111</v>
+        <v>6821142</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17846,22 +17860,22 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17888,7 +17902,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129128766</v>
+        <v>129128817</v>
       </c>
       <c r="B161" t="n">
         <v>79039</v>
@@ -17923,10 +17937,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445642</v>
+        <v>445832</v>
       </c>
       <c r="R161" t="n">
-        <v>6821136</v>
+        <v>6820988</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17953,22 +17967,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17995,7 +18009,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129128938</v>
+        <v>129128754</v>
       </c>
       <c r="B162" t="n">
         <v>79039</v>
@@ -18030,10 +18044,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>446479</v>
+        <v>445736</v>
       </c>
       <c r="R162" t="n">
-        <v>6821399</v>
+        <v>6821111</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18060,22 +18074,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18102,7 +18116,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129128740</v>
+        <v>129128766</v>
       </c>
       <c r="B163" t="n">
         <v>79039</v>
@@ -18131,21 +18145,16 @@
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>445688</v>
+        <v>445642</v>
       </c>
       <c r="R163" t="n">
-        <v>6821115</v>
+        <v>6821136</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18177,7 +18186,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18187,7 +18196,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18214,7 +18223,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129128778</v>
+        <v>129128938</v>
       </c>
       <c r="B164" t="n">
         <v>79039</v>
@@ -18249,10 +18258,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>445678</v>
+        <v>446479</v>
       </c>
       <c r="R164" t="n">
-        <v>6821292</v>
+        <v>6821399</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18279,22 +18288,22 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18321,10 +18330,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129129049</v>
+        <v>129128740</v>
       </c>
       <c r="B165" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18332,27 +18341,27 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -18361,10 +18370,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>446437</v>
+        <v>445688</v>
       </c>
       <c r="R165" t="n">
-        <v>6821476</v>
+        <v>6821115</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18391,22 +18400,22 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18433,54 +18442,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129128713</v>
+        <v>129128778</v>
       </c>
       <c r="B166" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>445994</v>
+        <v>445678</v>
       </c>
       <c r="R166" t="n">
-        <v>6821055</v>
+        <v>6821292</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18507,22 +18507,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -26972,10 +26972,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129128984</v>
+        <v>129128599</v>
       </c>
       <c r="B245" t="n">
-        <v>79039</v>
+        <v>83015</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26983,21 +26983,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27007,10 +27007,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>446554</v>
+        <v>445989</v>
       </c>
       <c r="R245" t="n">
-        <v>6821245</v>
+        <v>6821071</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27079,7 +27079,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129128877</v>
+        <v>129128885</v>
       </c>
       <c r="B246" t="n">
         <v>79039</v>
@@ -27114,10 +27114,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445750</v>
+        <v>445769</v>
       </c>
       <c r="R246" t="n">
-        <v>6821192</v>
+        <v>6821408</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -27159,7 +27159,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27186,7 +27186,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129129018</v>
+        <v>129128852</v>
       </c>
       <c r="B247" t="n">
         <v>79039</v>
@@ -27221,10 +27221,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445989</v>
+        <v>446021</v>
       </c>
       <c r="R247" t="n">
-        <v>6821243</v>
+        <v>6821061</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27256,7 +27256,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27293,7 +27293,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129128792</v>
+        <v>129128962</v>
       </c>
       <c r="B248" t="n">
         <v>79039</v>
@@ -27328,10 +27328,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445781</v>
+        <v>446377</v>
       </c>
       <c r="R248" t="n">
-        <v>6821123</v>
+        <v>6821364</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -27373,7 +27373,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -27400,7 +27400,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129128793</v>
+        <v>129128798</v>
       </c>
       <c r="B249" t="n">
         <v>79039</v>
@@ -27435,10 +27435,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445784</v>
+        <v>445860</v>
       </c>
       <c r="R249" t="n">
-        <v>6821130</v>
+        <v>6821067</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -27470,7 +27470,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -27480,7 +27480,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27507,7 +27507,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129128929</v>
+        <v>129128934</v>
       </c>
       <c r="B250" t="n">
         <v>79039</v>
@@ -27542,10 +27542,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>446509</v>
+        <v>446492</v>
       </c>
       <c r="R250" t="n">
-        <v>6821536</v>
+        <v>6821467</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -27577,7 +27577,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -27587,7 +27587,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -27614,45 +27614,54 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129128936</v>
+        <v>129128728</v>
       </c>
       <c r="B251" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>446493</v>
+        <v>446339</v>
       </c>
       <c r="R251" t="n">
-        <v>6821436</v>
+        <v>6821429</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -27684,7 +27693,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -27694,7 +27703,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -27721,7 +27730,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129128997</v>
+        <v>129128984</v>
       </c>
       <c r="B252" t="n">
         <v>79039</v>
@@ -27756,10 +27765,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>446356</v>
+        <v>446554</v>
       </c>
       <c r="R252" t="n">
-        <v>6821295</v>
+        <v>6821245</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -27791,7 +27800,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -27801,7 +27810,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27828,7 +27837,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129128777</v>
+        <v>129128877</v>
       </c>
       <c r="B253" t="n">
         <v>79039</v>
@@ -27863,10 +27872,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>445677</v>
+        <v>445750</v>
       </c>
       <c r="R253" t="n">
-        <v>6821243</v>
+        <v>6821192</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -27893,22 +27902,22 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27935,7 +27944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129128739</v>
+        <v>129129018</v>
       </c>
       <c r="B254" t="n">
         <v>79039</v>
@@ -27970,10 +27979,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>445806</v>
+        <v>445989</v>
       </c>
       <c r="R254" t="n">
-        <v>6821124</v>
+        <v>6821243</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28005,7 +28014,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28015,12 +28024,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>08:41</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Rikligt på tallarnas stammar i området</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28047,10 +28051,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129128599</v>
+        <v>129128792</v>
       </c>
       <c r="B255" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28058,21 +28062,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -28082,10 +28086,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>445989</v>
+        <v>445781</v>
       </c>
       <c r="R255" t="n">
-        <v>6821071</v>
+        <v>6821123</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28117,7 +28121,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -28127,7 +28131,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -28154,7 +28158,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129128885</v>
+        <v>129128793</v>
       </c>
       <c r="B256" t="n">
         <v>79039</v>
@@ -28189,10 +28193,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>445769</v>
+        <v>445784</v>
       </c>
       <c r="R256" t="n">
-        <v>6821408</v>
+        <v>6821130</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28224,7 +28228,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -28234,7 +28238,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -28261,7 +28265,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129128852</v>
+        <v>129128929</v>
       </c>
       <c r="B257" t="n">
         <v>79039</v>
@@ -28296,10 +28300,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>446021</v>
+        <v>446509</v>
       </c>
       <c r="R257" t="n">
-        <v>6821061</v>
+        <v>6821536</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28331,7 +28335,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -28341,7 +28345,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -28368,7 +28372,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>129128962</v>
+        <v>129128936</v>
       </c>
       <c r="B258" t="n">
         <v>79039</v>
@@ -28403,10 +28407,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>446377</v>
+        <v>446493</v>
       </c>
       <c r="R258" t="n">
-        <v>6821364</v>
+        <v>6821436</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28438,7 +28442,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -28448,7 +28452,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -28475,7 +28479,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129128798</v>
+        <v>129128997</v>
       </c>
       <c r="B259" t="n">
         <v>79039</v>
@@ -28510,10 +28514,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>445860</v>
+        <v>446356</v>
       </c>
       <c r="R259" t="n">
-        <v>6821067</v>
+        <v>6821295</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28545,7 +28549,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -28555,7 +28559,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -28582,7 +28586,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129128934</v>
+        <v>129128777</v>
       </c>
       <c r="B260" t="n">
         <v>79039</v>
@@ -28617,10 +28621,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>446492</v>
+        <v>445677</v>
       </c>
       <c r="R260" t="n">
-        <v>6821467</v>
+        <v>6821243</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28647,22 +28651,22 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -28689,54 +28693,45 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129128728</v>
+        <v>129128739</v>
       </c>
       <c r="B261" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>446339</v>
+        <v>445806</v>
       </c>
       <c r="R261" t="n">
-        <v>6821429</v>
+        <v>6821124</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -28768,7 +28763,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -28778,7 +28773,12 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Rikligt på tallarnas stammar i området</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -28805,10 +28805,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129128958</v>
+        <v>129128601</v>
       </c>
       <c r="B262" t="n">
-        <v>79039</v>
+        <v>83015</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -28816,21 +28816,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -28840,10 +28840,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>446326</v>
+        <v>445802</v>
       </c>
       <c r="R262" t="n">
-        <v>6821397</v>
+        <v>6821229</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -28885,7 +28885,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28912,7 +28912,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129128842</v>
+        <v>129128879</v>
       </c>
       <c r="B263" t="n">
         <v>79039</v>
@@ -28947,10 +28947,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>445954</v>
+        <v>445783</v>
       </c>
       <c r="R263" t="n">
-        <v>6820997</v>
+        <v>6821218</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -28992,7 +28992,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29019,7 +29019,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129128801</v>
+        <v>129128949</v>
       </c>
       <c r="B264" t="n">
         <v>79039</v>
@@ -29054,10 +29054,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>445885</v>
+        <v>446276</v>
       </c>
       <c r="R264" t="n">
-        <v>6820977</v>
+        <v>6821475</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29089,7 +29089,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -29099,7 +29099,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29126,7 +29126,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129128863</v>
+        <v>129128935</v>
       </c>
       <c r="B265" t="n">
         <v>79039</v>
@@ -29161,10 +29161,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>445909</v>
+        <v>446480</v>
       </c>
       <c r="R265" t="n">
-        <v>6821072</v>
+        <v>6821450</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -29196,7 +29196,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -29206,7 +29206,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -29233,7 +29233,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>129128945</v>
+        <v>129128970</v>
       </c>
       <c r="B266" t="n">
         <v>79039</v>
@@ -29268,10 +29268,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>446358</v>
+        <v>446434</v>
       </c>
       <c r="R266" t="n">
-        <v>6821437</v>
+        <v>6821308</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29303,7 +29303,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -29313,7 +29313,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -29340,7 +29340,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129128894</v>
+        <v>129128958</v>
       </c>
       <c r="B267" t="n">
         <v>79039</v>
@@ -29375,10 +29375,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>445944</v>
+        <v>446326</v>
       </c>
       <c r="R267" t="n">
-        <v>6821470</v>
+        <v>6821397</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -29420,7 +29420,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -29447,7 +29447,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129128952</v>
+        <v>129128842</v>
       </c>
       <c r="B268" t="n">
         <v>79039</v>
@@ -29482,10 +29482,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>446307</v>
+        <v>445954</v>
       </c>
       <c r="R268" t="n">
-        <v>6821433</v>
+        <v>6820997</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -29517,7 +29517,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -29554,7 +29554,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129128881</v>
+        <v>129128801</v>
       </c>
       <c r="B269" t="n">
         <v>79039</v>
@@ -29589,10 +29589,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>445799</v>
+        <v>445885</v>
       </c>
       <c r="R269" t="n">
-        <v>6821228</v>
+        <v>6820977</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -29624,7 +29624,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -29634,7 +29634,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29661,7 +29661,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129128799</v>
+        <v>129128863</v>
       </c>
       <c r="B270" t="n">
         <v>79039</v>
@@ -29696,10 +29696,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>445891</v>
+        <v>445909</v>
       </c>
       <c r="R270" t="n">
-        <v>6821036</v>
+        <v>6821072</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -29731,7 +29731,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -29768,7 +29768,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129128767</v>
+        <v>129128945</v>
       </c>
       <c r="B271" t="n">
         <v>79039</v>
@@ -29803,10 +29803,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>445646</v>
+        <v>446358</v>
       </c>
       <c r="R271" t="n">
-        <v>6821138</v>
+        <v>6821437</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -29833,22 +29833,22 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29875,10 +29875,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129128601</v>
+        <v>129128894</v>
       </c>
       <c r="B272" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -29886,21 +29886,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -29910,10 +29910,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>445802</v>
+        <v>445944</v>
       </c>
       <c r="R272" t="n">
-        <v>6821229</v>
+        <v>6821470</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -29945,7 +29945,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29982,7 +29982,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129128879</v>
+        <v>129128952</v>
       </c>
       <c r="B273" t="n">
         <v>79039</v>
@@ -30017,10 +30017,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>445783</v>
+        <v>446307</v>
       </c>
       <c r="R273" t="n">
-        <v>6821218</v>
+        <v>6821433</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -30062,7 +30062,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30089,7 +30089,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129128949</v>
+        <v>129128881</v>
       </c>
       <c r="B274" t="n">
         <v>79039</v>
@@ -30124,10 +30124,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>446276</v>
+        <v>445799</v>
       </c>
       <c r="R274" t="n">
-        <v>6821475</v>
+        <v>6821228</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30159,7 +30159,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30196,7 +30196,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129128935</v>
+        <v>129128799</v>
       </c>
       <c r="B275" t="n">
         <v>79039</v>
@@ -30231,10 +30231,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>446480</v>
+        <v>445891</v>
       </c>
       <c r="R275" t="n">
-        <v>6821450</v>
+        <v>6821036</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -30266,7 +30266,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -30303,7 +30303,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129128970</v>
+        <v>129128767</v>
       </c>
       <c r="B276" t="n">
         <v>79039</v>
@@ -30338,10 +30338,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>446434</v>
+        <v>445646</v>
       </c>
       <c r="R276" t="n">
-        <v>6821308</v>
+        <v>6821138</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -30368,22 +30368,22 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -30638,42 +30638,38 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129128725</v>
+        <v>129128647</v>
       </c>
       <c r="B279" t="n">
-        <v>98669</v>
+        <v>57722</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
@@ -30682,10 +30678,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>446020</v>
+        <v>445869</v>
       </c>
       <c r="R279" t="n">
-        <v>6821067</v>
+        <v>6821449</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -30717,7 +30713,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -30727,7 +30723,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -30754,54 +30750,53 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129128724</v>
+        <v>129128731</v>
       </c>
       <c r="B280" t="n">
-        <v>98669</v>
+        <v>56906</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>446021</v>
+        <v>445973</v>
       </c>
       <c r="R280" t="n">
-        <v>6821073</v>
+        <v>6821001</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -30833,7 +30828,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -30843,7 +30838,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30870,7 +30865,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129128701</v>
+        <v>129128725</v>
       </c>
       <c r="B281" t="n">
         <v>98669</v>
@@ -30900,7 +30895,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -30914,10 +30909,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>446332</v>
+        <v>446020</v>
       </c>
       <c r="R281" t="n">
-        <v>6821396</v>
+        <v>6821067</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -30949,7 +30944,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -30959,7 +30954,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30986,45 +30981,54 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129128843</v>
+        <v>129128724</v>
       </c>
       <c r="B282" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>445959</v>
+        <v>446021</v>
       </c>
       <c r="R282" t="n">
-        <v>6821028</v>
+        <v>6821073</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -31056,7 +31060,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -31066,7 +31070,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -31093,45 +31097,54 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129128963</v>
+        <v>129128701</v>
       </c>
       <c r="B283" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P283" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>446391</v>
+        <v>446332</v>
       </c>
       <c r="R283" t="n">
-        <v>6821355</v>
+        <v>6821396</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -31163,7 +31176,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -31173,7 +31186,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -31200,7 +31213,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>129128735</v>
+        <v>129128843</v>
       </c>
       <c r="B284" t="n">
         <v>79039</v>
@@ -31235,10 +31248,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>445835</v>
+        <v>445959</v>
       </c>
       <c r="R284" t="n">
-        <v>6821044</v>
+        <v>6821028</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -31270,7 +31283,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -31280,7 +31293,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -31307,7 +31320,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129129000</v>
+        <v>129128963</v>
       </c>
       <c r="B285" t="n">
         <v>79039</v>
@@ -31342,10 +31355,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>446264</v>
+        <v>446391</v>
       </c>
       <c r="R285" t="n">
-        <v>6821319</v>
+        <v>6821355</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -31377,7 +31390,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -31387,7 +31400,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -31414,7 +31427,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129129008</v>
+        <v>129128735</v>
       </c>
       <c r="B286" t="n">
         <v>79039</v>
@@ -31449,10 +31462,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>446191</v>
+        <v>445835</v>
       </c>
       <c r="R286" t="n">
-        <v>6821185</v>
+        <v>6821044</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -31484,7 +31497,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -31494,7 +31507,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -31521,7 +31534,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129128896</v>
+        <v>129129000</v>
       </c>
       <c r="B287" t="n">
         <v>79039</v>
@@ -31556,10 +31569,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>445967</v>
+        <v>446264</v>
       </c>
       <c r="R287" t="n">
-        <v>6821468</v>
+        <v>6821319</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -31591,7 +31604,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -31601,7 +31614,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -31628,7 +31641,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>129128824</v>
+        <v>129129008</v>
       </c>
       <c r="B288" t="n">
         <v>79039</v>
@@ -31663,10 +31676,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>445860</v>
+        <v>446191</v>
       </c>
       <c r="R288" t="n">
-        <v>6821017</v>
+        <v>6821185</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -31698,7 +31711,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -31708,7 +31721,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -31735,7 +31748,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>129128923</v>
+        <v>129128896</v>
       </c>
       <c r="B289" t="n">
         <v>79039</v>
@@ -31770,10 +31783,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>446298</v>
+        <v>445967</v>
       </c>
       <c r="R289" t="n">
-        <v>6821529</v>
+        <v>6821468</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -31805,7 +31818,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -31815,7 +31828,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -31842,10 +31855,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>129128695</v>
+        <v>129128824</v>
       </c>
       <c r="B290" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -31853,21 +31866,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -31877,10 +31890,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>445706</v>
+        <v>445860</v>
       </c>
       <c r="R290" t="n">
-        <v>6821069</v>
+        <v>6821017</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -31907,22 +31920,22 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -31949,7 +31962,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>129128992</v>
+        <v>129128923</v>
       </c>
       <c r="B291" t="n">
         <v>79039</v>
@@ -31984,10 +31997,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>446420</v>
+        <v>446298</v>
       </c>
       <c r="R291" t="n">
-        <v>6821284</v>
+        <v>6821529</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -32019,7 +32032,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -32029,7 +32042,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -32056,10 +32069,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>129128596</v>
+        <v>129128695</v>
       </c>
       <c r="B292" t="n">
-        <v>83015</v>
+        <v>78796</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32067,21 +32080,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -32091,10 +32104,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>445733</v>
+        <v>445706</v>
       </c>
       <c r="R292" t="n">
-        <v>6821108</v>
+        <v>6821069</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32126,7 +32139,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -32136,7 +32149,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -32163,10 +32176,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>129129064</v>
+        <v>129128992</v>
       </c>
       <c r="B293" t="n">
-        <v>78442</v>
+        <v>79039</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32174,21 +32187,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -32198,10 +32211,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>445673</v>
+        <v>446420</v>
       </c>
       <c r="R293" t="n">
-        <v>6821223</v>
+        <v>6821284</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -32228,22 +32241,22 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -32270,10 +32283,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>129128990</v>
+        <v>129128596</v>
       </c>
       <c r="B294" t="n">
-        <v>79039</v>
+        <v>83015</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32281,21 +32294,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -32305,10 +32318,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>446441</v>
+        <v>445733</v>
       </c>
       <c r="R294" t="n">
-        <v>6821271</v>
+        <v>6821108</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -32335,22 +32348,22 @@
       </c>
       <c r="Y294" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -32377,10 +32390,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>129128647</v>
+        <v>129129064</v>
       </c>
       <c r="B295" t="n">
-        <v>57722</v>
+        <v>78442</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32388,39 +32401,34 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P295" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>445869</v>
+        <v>445673</v>
       </c>
       <c r="R295" t="n">
-        <v>6821449</v>
+        <v>6821223</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -32447,22 +32455,22 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -32489,10 +32497,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>129128731</v>
+        <v>129128990</v>
       </c>
       <c r="B296" t="n">
-        <v>56906</v>
+        <v>79039</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32500,42 +32508,34 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>445973</v>
+        <v>446441</v>
       </c>
       <c r="R296" t="n">
-        <v>6821001</v>
+        <v>6821271</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -32567,7 +32567,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -32577,7 +32577,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -33353,54 +33353,45 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>129129054</v>
+        <v>129128773</v>
       </c>
       <c r="B304" t="n">
-        <v>92862</v>
+        <v>79039</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>446135</v>
+        <v>445688</v>
       </c>
       <c r="R304" t="n">
-        <v>6821160</v>
+        <v>6821162</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -33427,22 +33418,22 @@
       </c>
       <c r="Y304" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -33469,10 +33460,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>129128637</v>
+        <v>129128698</v>
       </c>
       <c r="B305" t="n">
-        <v>57722</v>
+        <v>78796</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -33480,39 +33471,34 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>445753</v>
+        <v>446294</v>
       </c>
       <c r="R305" t="n">
-        <v>6821059</v>
+        <v>6821320</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -33539,22 +33525,22 @@
       </c>
       <c r="Y305" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -33581,10 +33567,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>129128732</v>
+        <v>129128593</v>
       </c>
       <c r="B306" t="n">
-        <v>56906</v>
+        <v>79658</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -33592,39 +33578,34 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>445798</v>
+        <v>445713</v>
       </c>
       <c r="R306" t="n">
-        <v>6821116</v>
+        <v>6821074</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -33651,22 +33632,22 @@
       </c>
       <c r="Y306" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -33693,50 +33674,45 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>129129066</v>
+        <v>129128883</v>
       </c>
       <c r="B307" t="n">
-        <v>5177</v>
+        <v>79039</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>446400</v>
+        <v>445744</v>
       </c>
       <c r="R307" t="n">
-        <v>6821290</v>
+        <v>6821381</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -33768,7 +33744,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -33778,7 +33754,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33805,32 +33781,32 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>129128661</v>
+        <v>129128749</v>
       </c>
       <c r="B308" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -33840,10 +33816,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>445730</v>
+        <v>445713</v>
       </c>
       <c r="R308" t="n">
-        <v>6821049</v>
+        <v>6821075</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -33875,7 +33851,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -33885,12 +33861,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>Intill järnoxidkälla</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33917,32 +33888,32 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>129128674</v>
+        <v>129128968</v>
       </c>
       <c r="B309" t="n">
-        <v>97546</v>
+        <v>79039</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -33952,10 +33923,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>446442</v>
+        <v>446431</v>
       </c>
       <c r="R309" t="n">
-        <v>6821270</v>
+        <v>6821318</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -33987,7 +33958,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -33997,7 +33968,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -34024,7 +33995,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>129128773</v>
+        <v>129128871</v>
       </c>
       <c r="B310" t="n">
         <v>79039</v>
@@ -34059,10 +34030,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>445688</v>
+        <v>445736</v>
       </c>
       <c r="R310" t="n">
-        <v>6821162</v>
+        <v>6821151</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -34089,22 +34060,22 @@
       </c>
       <c r="Y310" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -34131,10 +34102,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>129128698</v>
+        <v>129128600</v>
       </c>
       <c r="B311" t="n">
-        <v>78796</v>
+        <v>83015</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34142,21 +34113,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -34166,10 +34137,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>446294</v>
+        <v>445735</v>
       </c>
       <c r="R311" t="n">
-        <v>6821320</v>
+        <v>6821150</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -34201,7 +34172,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -34211,7 +34182,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -34238,10 +34209,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>129128593</v>
+        <v>129128732</v>
       </c>
       <c r="B312" t="n">
-        <v>79658</v>
+        <v>56906</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -34249,34 +34220,39 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P312" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>445713</v>
+        <v>445798</v>
       </c>
       <c r="R312" t="n">
-        <v>6821074</v>
+        <v>6821116</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -34303,22 +34279,22 @@
       </c>
       <c r="Y312" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -34345,45 +34321,50 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>129128883</v>
+        <v>129129066</v>
       </c>
       <c r="B313" t="n">
-        <v>79039</v>
+        <v>5177</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P313" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>445744</v>
+        <v>446400</v>
       </c>
       <c r="R313" t="n">
-        <v>6821381</v>
+        <v>6821290</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -34415,7 +34396,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -34425,7 +34406,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -34452,32 +34433,32 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>129128749</v>
+        <v>129128691</v>
       </c>
       <c r="B314" t="n">
-        <v>79039</v>
+        <v>58095</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -34487,10 +34468,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>445713</v>
+        <v>446264</v>
       </c>
       <c r="R314" t="n">
-        <v>6821075</v>
+        <v>6821575</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -34517,22 +34498,22 @@
       </c>
       <c r="Y314" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -34559,45 +34540,54 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>129128968</v>
+        <v>129129054</v>
       </c>
       <c r="B315" t="n">
-        <v>79039</v>
+        <v>92862</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P315" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>446431</v>
+        <v>446135</v>
       </c>
       <c r="R315" t="n">
-        <v>6821318</v>
+        <v>6821160</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -34629,7 +34619,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -34639,7 +34629,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -34666,10 +34656,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>129128871</v>
+        <v>129128637</v>
       </c>
       <c r="B316" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -34677,34 +34667,39 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P316" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>445736</v>
+        <v>445753</v>
       </c>
       <c r="R316" t="n">
-        <v>6821151</v>
+        <v>6821059</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -34731,22 +34726,22 @@
       </c>
       <c r="Y316" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -34773,32 +34768,32 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>129128600</v>
+        <v>129128661</v>
       </c>
       <c r="B317" t="n">
-        <v>83015</v>
+        <v>97540</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -34808,10 +34803,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>445735</v>
+        <v>445730</v>
       </c>
       <c r="R317" t="n">
-        <v>6821150</v>
+        <v>6821049</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -34838,22 +34833,27 @@
       </c>
       <c r="Y317" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>Intill järnoxidkälla</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -34880,10 +34880,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>129128691</v>
+        <v>129128674</v>
       </c>
       <c r="B318" t="n">
-        <v>58095</v>
+        <v>97546</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34891,21 +34891,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>103015</v>
+        <v>221941</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
@@ -34915,10 +34915,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>446264</v>
+        <v>446442</v>
       </c>
       <c r="R318" t="n">
-        <v>6821575</v>
+        <v>6821270</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -34950,7 +34950,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -34960,7 +34960,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD318" t="b">

--- a/artfynd/A 47442-2025 artfynd.xlsx
+++ b/artfynd/A 47442-2025 artfynd.xlsx
@@ -34990,7 +34990,7 @@
         <v>129129059</v>
       </c>
       <c r="B319" t="n">
-        <v>87021</v>
+        <v>87027</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 47442-2025 artfynd.xlsx
+++ b/artfynd/A 47442-2025 artfynd.xlsx
@@ -34990,7 +34990,7 @@
         <v>129129059</v>
       </c>
       <c r="B319" t="n">
-        <v>87027</v>
+        <v>87028</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 47442-2025 artfynd.xlsx
+++ b/artfynd/A 47442-2025 artfynd.xlsx
@@ -34990,7 +34990,7 @@
         <v>129129059</v>
       </c>
       <c r="B319" t="n">
-        <v>87028</v>
+        <v>87033</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 47442-2025 artfynd.xlsx
+++ b/artfynd/A 47442-2025 artfynd.xlsx
@@ -34990,7 +34990,7 @@
         <v>129129059</v>
       </c>
       <c r="B319" t="n">
-        <v>87033</v>
+        <v>87037</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
